--- a/NYD_data/NYD_sampleinfo.xlsx
+++ b/NYD_data/NYD_sampleinfo.xlsx
@@ -1533,9 +1533,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -1601,16 +1601,16 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -1622,34 +1622,34 @@
         <v>23</v>
       </c>
       <c r="H2">
-        <v>65.1</v>
+        <v>81.6</v>
       </c>
       <c r="I2">
-        <v>1.99</v>
+        <v>2.58</v>
       </c>
       <c r="J2">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="K2">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="L2">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="M2">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="N2">
-        <v>17.7</v>
+        <v>16.1</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
       </c>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R2" t="s">
         <v>27</v>
@@ -1657,16 +1657,16 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -1678,34 +1678,34 @@
         <v>23</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>70.9</v>
       </c>
       <c r="I3">
-        <v>1.51</v>
+        <v>2.21</v>
       </c>
       <c r="J3">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="N3">
-        <v>20</v>
+        <v>17.1</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
       </c>
       <c r="P3" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R3" t="s">
         <v>27</v>
@@ -1713,16 +1713,16 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -1734,34 +1734,34 @@
         <v>23</v>
       </c>
       <c r="H4">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="I4">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J4">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="K4">
         <v>1.2</v>
       </c>
       <c r="L4">
-        <v>8.5</v>
+        <v>8.3</v>
       </c>
       <c r="M4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N4">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>
       </c>
       <c r="P4" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R4" t="s">
         <v>27</v>
@@ -1769,16 +1769,16 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -1790,34 +1790,34 @@
         <v>23</v>
       </c>
       <c r="H5">
-        <v>40.9</v>
+        <v>55.2</v>
       </c>
       <c r="I5">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="J5">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="K5">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="L5">
-        <v>12.2</v>
+        <v>9.1</v>
       </c>
       <c r="M5">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="N5">
-        <v>22.2</v>
+        <v>19.1</v>
       </c>
       <c r="O5" t="s">
         <v>24</v>
       </c>
       <c r="P5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R5" t="s">
         <v>27</v>
@@ -1825,16 +1825,16 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -1846,34 +1846,34 @@
         <v>23</v>
       </c>
       <c r="H6">
-        <v>53.9</v>
+        <v>54.8</v>
       </c>
       <c r="I6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J6">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="K6">
         <v>1.1</v>
       </c>
       <c r="L6">
-        <v>9.3</v>
+        <v>9.1</v>
       </c>
       <c r="M6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N6">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="O6" t="s">
         <v>24</v>
       </c>
       <c r="P6" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R6" t="s">
         <v>27</v>
@@ -1881,16 +1881,16 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -1902,34 +1902,34 @@
         <v>23</v>
       </c>
       <c r="H7">
-        <v>57</v>
+        <v>72.1</v>
       </c>
       <c r="I7">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="J7">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="K7">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="L7">
-        <v>8.8</v>
+        <v>6.9</v>
       </c>
       <c r="M7">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N7">
-        <v>18.8</v>
+        <v>16.9</v>
       </c>
       <c r="O7" t="s">
         <v>24</v>
       </c>
       <c r="P7" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R7" t="s">
         <v>27</v>
@@ -1937,16 +1937,16 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -1958,34 +1958,34 @@
         <v>23</v>
       </c>
       <c r="H8">
-        <v>92.1</v>
+        <v>63.2</v>
       </c>
       <c r="I8">
-        <v>2.85</v>
+        <v>2.01</v>
       </c>
       <c r="J8">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="K8">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="L8">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="M8">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="N8">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="O8" t="s">
         <v>24</v>
       </c>
       <c r="P8" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q8" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R8" t="s">
         <v>27</v>
@@ -1993,16 +1993,16 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -2014,34 +2014,34 @@
         <v>23</v>
       </c>
       <c r="H9">
-        <v>111.1</v>
+        <v>64.1</v>
       </c>
       <c r="I9">
-        <v>3.43</v>
+        <v>2.03</v>
       </c>
       <c r="J9">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="K9">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="L9">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="M9">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="N9">
-        <v>14.5</v>
+        <v>17.8</v>
       </c>
       <c r="O9" t="s">
         <v>24</v>
       </c>
       <c r="P9" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="Q9" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="R9" t="s">
         <v>27</v>
@@ -2049,16 +2049,16 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -2070,34 +2070,34 @@
         <v>23</v>
       </c>
       <c r="H10">
-        <v>60.2</v>
+        <v>87.6</v>
       </c>
       <c r="I10">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="J10">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="K10">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="L10">
-        <v>8.3</v>
+        <v>5.7</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="N10">
-        <v>18.3</v>
+        <v>15.7</v>
       </c>
       <c r="O10" t="s">
         <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R10" t="s">
         <v>27</v>
@@ -2105,16 +2105,16 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11">
         <v>18</v>
       </c>
-      <c r="B11">
-        <v>26</v>
-      </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -2126,34 +2126,34 @@
         <v>23</v>
       </c>
       <c r="H11">
-        <v>138.5</v>
+        <v>43.9</v>
       </c>
       <c r="I11">
-        <v>5.07</v>
+        <v>1.47</v>
       </c>
       <c r="J11">
-        <v>1.11</v>
+        <v>0.18</v>
       </c>
       <c r="K11">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="L11">
-        <v>3.6</v>
+        <v>11.4</v>
       </c>
       <c r="M11">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="N11">
-        <v>13.6</v>
+        <v>21.4</v>
       </c>
       <c r="O11" t="s">
         <v>24</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R11" t="s">
         <v>27</v>
@@ -2161,16 +2161,16 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -2182,34 +2182,34 @@
         <v>23</v>
       </c>
       <c r="H12">
-        <v>68.6</v>
+        <v>39.1</v>
       </c>
       <c r="I12">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="J12">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="K12">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="L12">
-        <v>7.3</v>
+        <v>12.8</v>
       </c>
       <c r="M12">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="N12">
-        <v>17.3</v>
+        <v>22.8</v>
       </c>
       <c r="O12" t="s">
         <v>24</v>
       </c>
       <c r="P12" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R12" t="s">
         <v>27</v>
@@ -2217,16 +2217,16 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B13">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
@@ -2238,34 +2238,34 @@
         <v>23</v>
       </c>
       <c r="H13">
-        <v>53</v>
+        <v>60.3</v>
       </c>
       <c r="I13">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="J13">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="K13">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L13">
-        <v>9.4</v>
+        <v>8.3</v>
       </c>
       <c r="M13">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
       <c r="O13" t="s">
         <v>24</v>
       </c>
       <c r="P13" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q13" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R13" t="s">
         <v>27</v>
@@ -2273,16 +2273,16 @@
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -2294,34 +2294,34 @@
         <v>23</v>
       </c>
       <c r="H14">
-        <v>54.8</v>
+        <v>26.6</v>
       </c>
       <c r="I14">
-        <v>1.62</v>
+        <v>0.88</v>
       </c>
       <c r="J14">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="K14">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="L14">
-        <v>9.1</v>
+        <v>18.8</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="N14">
-        <v>19.1</v>
+        <v>28.8</v>
       </c>
       <c r="O14" t="s">
         <v>24</v>
       </c>
       <c r="P14" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R14" t="s">
         <v>27</v>
@@ -2329,16 +2329,16 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B15">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
@@ -2350,34 +2350,34 @@
         <v>23</v>
       </c>
       <c r="H15">
-        <v>121.9</v>
+        <v>56.9</v>
       </c>
       <c r="I15">
-        <v>3.77</v>
+        <v>1.85</v>
       </c>
       <c r="J15">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="K15">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="L15">
-        <v>4.1</v>
+        <v>8.8</v>
       </c>
       <c r="M15">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="N15">
-        <v>14.1</v>
+        <v>18.8</v>
       </c>
       <c r="O15" t="s">
         <v>24</v>
       </c>
       <c r="P15" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q15" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R15" t="s">
         <v>27</v>
@@ -2385,16 +2385,16 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B16">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -2406,34 +2406,34 @@
         <v>23</v>
       </c>
       <c r="H16">
-        <v>68.8</v>
+        <v>37.3</v>
       </c>
       <c r="I16">
-        <v>2.12</v>
+        <v>1.23</v>
       </c>
       <c r="J16">
-        <v>0.07</v>
+        <v>0.12</v>
       </c>
       <c r="K16">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="L16">
-        <v>7.3</v>
+        <v>13.4</v>
       </c>
       <c r="M16">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="N16">
-        <v>17.3</v>
+        <v>23.4</v>
       </c>
       <c r="O16" t="s">
         <v>24</v>
       </c>
       <c r="P16" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R16" t="s">
         <v>27</v>
@@ -2441,16 +2441,16 @@
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
@@ -2462,1385 +2462,41 @@
         <v>23</v>
       </c>
       <c r="H17">
-        <v>99.4</v>
+        <v>35.3</v>
       </c>
       <c r="I17">
-        <v>3.09</v>
+        <v>1.14</v>
       </c>
       <c r="J17">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>14.2</v>
       </c>
       <c r="M17">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="N17">
-        <v>15</v>
+        <v>24.2</v>
       </c>
       <c r="O17" t="s">
         <v>24</v>
       </c>
       <c r="P17" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="R17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
-      <c r="A18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18">
-        <v>44.9</v>
-      </c>
-      <c r="I18">
-        <v>1.38</v>
-      </c>
-      <c r="J18">
-        <v>0.03</v>
-      </c>
-      <c r="K18">
-        <v>0.9</v>
-      </c>
-      <c r="L18">
-        <v>11.1</v>
-      </c>
-      <c r="M18">
-        <v>4.5</v>
-      </c>
-      <c r="N18">
-        <v>21.1</v>
-      </c>
-      <c r="O18" t="s">
-        <v>24</v>
-      </c>
-      <c r="P18" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>62</v>
-      </c>
-      <c r="R18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19">
-        <v>44.9</v>
-      </c>
-      <c r="I19">
-        <v>1.35</v>
-      </c>
-      <c r="J19">
-        <v>0.02</v>
-      </c>
-      <c r="K19">
-        <v>0.9</v>
-      </c>
-      <c r="L19">
-        <v>11.1</v>
-      </c>
-      <c r="M19">
-        <v>4.5</v>
-      </c>
-      <c r="N19">
-        <v>21.1</v>
-      </c>
-      <c r="O19" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>62</v>
-      </c>
-      <c r="R19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20">
-        <v>11</v>
-      </c>
-      <c r="C20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20">
-        <v>48.6</v>
-      </c>
-      <c r="I20">
-        <v>1.48</v>
-      </c>
-      <c r="J20">
-        <v>0.03</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>10.3</v>
-      </c>
-      <c r="M20">
-        <v>4.1</v>
-      </c>
-      <c r="N20">
-        <v>20.3</v>
-      </c>
-      <c r="O20" t="s">
-        <v>24</v>
-      </c>
-      <c r="P20" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>62</v>
-      </c>
-      <c r="R20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21">
-        <v>47</v>
-      </c>
-      <c r="I21">
-        <v>1.47</v>
-      </c>
-      <c r="J21">
-        <v>0.05</v>
-      </c>
-      <c r="K21">
-        <v>0.9</v>
-      </c>
-      <c r="L21">
-        <v>10.6</v>
-      </c>
-      <c r="M21">
-        <v>4.3</v>
-      </c>
-      <c r="N21">
-        <v>20.6</v>
-      </c>
-      <c r="O21" t="s">
-        <v>24</v>
-      </c>
-      <c r="P21" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>62</v>
-      </c>
-      <c r="R21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22">
-        <v>48.3</v>
-      </c>
-      <c r="I22">
-        <v>1.5</v>
-      </c>
-      <c r="J22">
-        <v>0.05</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>10.4</v>
-      </c>
-      <c r="M22">
-        <v>4.1</v>
-      </c>
-      <c r="N22">
-        <v>20.4</v>
-      </c>
-      <c r="O22" t="s">
-        <v>24</v>
-      </c>
-      <c r="P22" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>62</v>
-      </c>
-      <c r="R22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23">
-        <v>45.5</v>
-      </c>
-      <c r="I23">
-        <v>1.41</v>
-      </c>
-      <c r="J23">
-        <v>0.05</v>
-      </c>
-      <c r="K23">
-        <v>0.9</v>
-      </c>
-      <c r="L23">
-        <v>11</v>
-      </c>
-      <c r="M23">
-        <v>4.4</v>
-      </c>
-      <c r="N23">
-        <v>21</v>
-      </c>
-      <c r="O23" t="s">
-        <v>24</v>
-      </c>
-      <c r="P23" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>62</v>
-      </c>
-      <c r="R23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24">
-        <v>15</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24">
-        <v>54.1</v>
-      </c>
-      <c r="I24">
-        <v>1.57</v>
-      </c>
-      <c r="J24">
-        <v>0.08</v>
-      </c>
-      <c r="K24">
-        <v>1.1</v>
-      </c>
-      <c r="L24">
-        <v>9.2</v>
-      </c>
-      <c r="M24">
-        <v>3.7</v>
-      </c>
-      <c r="N24">
-        <v>19.2</v>
-      </c>
-      <c r="O24" t="s">
-        <v>24</v>
-      </c>
-      <c r="P24" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>62</v>
-      </c>
-      <c r="R24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25">
-        <v>80.5</v>
-      </c>
-      <c r="I25">
-        <v>2.48</v>
-      </c>
-      <c r="J25">
-        <v>0.06</v>
-      </c>
-      <c r="K25">
-        <v>1.6</v>
-      </c>
-      <c r="L25">
-        <v>6.2</v>
-      </c>
-      <c r="M25">
-        <v>2.5</v>
-      </c>
-      <c r="N25">
-        <v>16.2</v>
-      </c>
-      <c r="O25" t="s">
-        <v>24</v>
-      </c>
-      <c r="P25" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>62</v>
-      </c>
-      <c r="R25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
-      <c r="A26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26">
-        <v>81.6</v>
-      </c>
-      <c r="I26">
-        <v>2.58</v>
-      </c>
-      <c r="J26">
-        <v>0.14</v>
-      </c>
-      <c r="K26">
-        <v>1.6</v>
-      </c>
-      <c r="L26">
-        <v>6.1</v>
-      </c>
-      <c r="M26">
-        <v>2.5</v>
-      </c>
-      <c r="N26">
-        <v>16.1</v>
-      </c>
-      <c r="O26" t="s">
-        <v>24</v>
-      </c>
-      <c r="P26" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>80</v>
-      </c>
-      <c r="R26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
-      <c r="A27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27">
-        <v>70.9</v>
-      </c>
-      <c r="I27">
-        <v>2.21</v>
-      </c>
-      <c r="J27">
-        <v>0.09</v>
-      </c>
-      <c r="K27">
-        <v>1.4</v>
-      </c>
-      <c r="L27">
-        <v>7.1</v>
-      </c>
-      <c r="M27">
-        <v>2.8</v>
-      </c>
-      <c r="N27">
-        <v>17.1</v>
-      </c>
-      <c r="O27" t="s">
-        <v>24</v>
-      </c>
-      <c r="P27" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>80</v>
-      </c>
-      <c r="R27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28">
-        <v>60.5</v>
-      </c>
-      <c r="I28">
-        <v>1.9</v>
-      </c>
-      <c r="J28">
-        <v>0.09</v>
-      </c>
-      <c r="K28">
-        <v>1.2</v>
-      </c>
-      <c r="L28">
-        <v>8.3</v>
-      </c>
-      <c r="M28">
-        <v>3.3</v>
-      </c>
-      <c r="N28">
-        <v>18.3</v>
-      </c>
-      <c r="O28" t="s">
-        <v>24</v>
-      </c>
-      <c r="P28" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>80</v>
-      </c>
-      <c r="R28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29">
-        <v>55.2</v>
-      </c>
-      <c r="I29">
-        <v>1.75</v>
-      </c>
-      <c r="J29">
-        <v>0.09</v>
-      </c>
-      <c r="K29">
-        <v>1.1</v>
-      </c>
-      <c r="L29">
-        <v>9.1</v>
-      </c>
-      <c r="M29">
-        <v>3.6</v>
-      </c>
-      <c r="N29">
-        <v>19.1</v>
-      </c>
-      <c r="O29" t="s">
-        <v>24</v>
-      </c>
-      <c r="P29" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>80</v>
-      </c>
-      <c r="R29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
-      <c r="A30" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30">
-        <v>54.8</v>
-      </c>
-      <c r="I30">
-        <v>1.7</v>
-      </c>
-      <c r="J30">
-        <v>0.02</v>
-      </c>
-      <c r="K30">
-        <v>1.1</v>
-      </c>
-      <c r="L30">
-        <v>9.1</v>
-      </c>
-      <c r="M30">
-        <v>3.6</v>
-      </c>
-      <c r="N30">
-        <v>19.1</v>
-      </c>
-      <c r="O30" t="s">
-        <v>24</v>
-      </c>
-      <c r="P30" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>80</v>
-      </c>
-      <c r="R30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31">
-        <v>72.1</v>
-      </c>
-      <c r="I31">
-        <v>2.28</v>
-      </c>
-      <c r="J31">
-        <v>0.1</v>
-      </c>
-      <c r="K31">
-        <v>1.4</v>
-      </c>
-      <c r="L31">
-        <v>6.9</v>
-      </c>
-      <c r="M31">
-        <v>2.8</v>
-      </c>
-      <c r="N31">
-        <v>16.9</v>
-      </c>
-      <c r="O31" t="s">
-        <v>24</v>
-      </c>
-      <c r="P31" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>80</v>
-      </c>
-      <c r="R31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H32">
-        <v>63.2</v>
-      </c>
-      <c r="I32">
-        <v>2.01</v>
-      </c>
-      <c r="J32">
-        <v>0.14</v>
-      </c>
-      <c r="K32">
-        <v>1.3</v>
-      </c>
-      <c r="L32">
-        <v>7.9</v>
-      </c>
-      <c r="M32">
-        <v>3.2</v>
-      </c>
-      <c r="N32">
-        <v>17.9</v>
-      </c>
-      <c r="O32" t="s">
-        <v>24</v>
-      </c>
-      <c r="P32" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>80</v>
-      </c>
-      <c r="R32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
-      <c r="A33" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33">
-        <v>64.1</v>
-      </c>
-      <c r="I33">
-        <v>2.03</v>
-      </c>
-      <c r="J33">
-        <v>0.13</v>
-      </c>
-      <c r="K33">
-        <v>1.3</v>
-      </c>
-      <c r="L33">
-        <v>7.8</v>
-      </c>
-      <c r="M33">
-        <v>3.1</v>
-      </c>
-      <c r="N33">
-        <v>17.8</v>
-      </c>
-      <c r="O33" t="s">
-        <v>24</v>
-      </c>
-      <c r="P33" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>80</v>
-      </c>
-      <c r="R33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34">
-        <v>87.6</v>
-      </c>
-      <c r="I34">
-        <v>2.8</v>
-      </c>
-      <c r="J34">
-        <v>0.18</v>
-      </c>
-      <c r="K34">
-        <v>1.8</v>
-      </c>
-      <c r="L34">
-        <v>5.7</v>
-      </c>
-      <c r="M34">
-        <v>2.3</v>
-      </c>
-      <c r="N34">
-        <v>15.7</v>
-      </c>
-      <c r="O34" t="s">
-        <v>24</v>
-      </c>
-      <c r="P34" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>98</v>
-      </c>
-      <c r="R34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
-      <c r="A35" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35">
-        <v>18</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35">
-        <v>43.9</v>
-      </c>
-      <c r="I35">
-        <v>1.47</v>
-      </c>
-      <c r="J35">
-        <v>0.18</v>
-      </c>
-      <c r="K35">
-        <v>0.9</v>
-      </c>
-      <c r="L35">
-        <v>11.4</v>
-      </c>
-      <c r="M35">
-        <v>4.6</v>
-      </c>
-      <c r="N35">
-        <v>21.4</v>
-      </c>
-      <c r="O35" t="s">
-        <v>24</v>
-      </c>
-      <c r="P35" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>98</v>
-      </c>
-      <c r="R35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
-      <c r="A36" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36">
-        <v>19</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F36" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36">
-        <v>39.1</v>
-      </c>
-      <c r="I36">
-        <v>1.24</v>
-      </c>
-      <c r="J36">
-        <v>0.1</v>
-      </c>
-      <c r="K36">
-        <v>0.8</v>
-      </c>
-      <c r="L36">
-        <v>12.8</v>
-      </c>
-      <c r="M36">
-        <v>5.1</v>
-      </c>
-      <c r="N36">
-        <v>22.8</v>
-      </c>
-      <c r="O36" t="s">
-        <v>24</v>
-      </c>
-      <c r="P36" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>98</v>
-      </c>
-      <c r="R36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
-      <c r="A37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37">
-        <v>20</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37">
-        <v>60.3</v>
-      </c>
-      <c r="I37">
-        <v>1.91</v>
-      </c>
-      <c r="J37">
-        <v>0.1</v>
-      </c>
-      <c r="K37">
-        <v>1.2</v>
-      </c>
-      <c r="L37">
-        <v>8.3</v>
-      </c>
-      <c r="M37">
-        <v>3.3</v>
-      </c>
-      <c r="N37">
-        <v>18.3</v>
-      </c>
-      <c r="O37" t="s">
-        <v>24</v>
-      </c>
-      <c r="P37" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>98</v>
-      </c>
-      <c r="R37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
-      <c r="A38" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38">
-        <v>21</v>
-      </c>
-      <c r="C38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38">
-        <v>26.6</v>
-      </c>
-      <c r="I38">
-        <v>0.88</v>
-      </c>
-      <c r="J38">
-        <v>0.07</v>
-      </c>
-      <c r="K38">
-        <v>0.5</v>
-      </c>
-      <c r="L38">
-        <v>18.8</v>
-      </c>
-      <c r="M38">
-        <v>7.5</v>
-      </c>
-      <c r="N38">
-        <v>28.8</v>
-      </c>
-      <c r="O38" t="s">
-        <v>24</v>
-      </c>
-      <c r="P38" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>98</v>
-      </c>
-      <c r="R38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
-      <c r="A39" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39">
-        <v>56.9</v>
-      </c>
-      <c r="I39">
-        <v>1.85</v>
-      </c>
-      <c r="J39">
-        <v>0.14</v>
-      </c>
-      <c r="K39">
-        <v>1.1</v>
-      </c>
-      <c r="L39">
-        <v>8.8</v>
-      </c>
-      <c r="M39">
-        <v>3.5</v>
-      </c>
-      <c r="N39">
-        <v>18.8</v>
-      </c>
-      <c r="O39" t="s">
-        <v>24</v>
-      </c>
-      <c r="P39" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>98</v>
-      </c>
-      <c r="R39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
-      <c r="A40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40">
-        <v>23</v>
-      </c>
-      <c r="C40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-      <c r="F40" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" t="s">
-        <v>23</v>
-      </c>
-      <c r="H40">
-        <v>37.3</v>
-      </c>
-      <c r="I40">
-        <v>1.23</v>
-      </c>
-      <c r="J40">
-        <v>0.12</v>
-      </c>
-      <c r="K40">
-        <v>0.7</v>
-      </c>
-      <c r="L40">
-        <v>13.4</v>
-      </c>
-      <c r="M40">
-        <v>5.4</v>
-      </c>
-      <c r="N40">
-        <v>23.4</v>
-      </c>
-      <c r="O40" t="s">
-        <v>24</v>
-      </c>
-      <c r="P40" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>98</v>
-      </c>
-      <c r="R40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41">
-        <v>24</v>
-      </c>
-      <c r="C41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" t="s">
-        <v>22</v>
-      </c>
-      <c r="G41" t="s">
-        <v>23</v>
-      </c>
-      <c r="H41">
-        <v>35.3</v>
-      </c>
-      <c r="I41">
-        <v>1.14</v>
-      </c>
-      <c r="J41">
-        <v>0.08</v>
-      </c>
-      <c r="K41">
-        <v>0.7</v>
-      </c>
-      <c r="L41">
-        <v>14.2</v>
-      </c>
-      <c r="M41">
-        <v>5.7</v>
-      </c>
-      <c r="N41">
-        <v>24.2</v>
-      </c>
-      <c r="O41" t="s">
-        <v>24</v>
-      </c>
-      <c r="P41" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>98</v>
-      </c>
-      <c r="R41" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:R41" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:R17" ns1:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
